--- a/lessons_learned.xlsx
+++ b/lessons_learned.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1058,7 +1058,56 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="50" customHeight="1"/>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8604</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Технічне</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Виконання</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Передумова: клієнту для оцінки та тесту було надіслано ЧОТИРИ геошурупи (2 NC 57 1000мм нав 650мм з буровими коронками; 2 N4 57 1000мм нав 650мм) ДВІ 5м збірні стійки (кожна з двох деталей), метизи та інструкцію з монтажу даних ГШ та стійок. Основне припущення на даному етапі було: Клієнт зможе самостійно вкрутити дані ГШ та змонтувати стійки без додатковою техніки та інструментів. Клієнт не зміг самостійно вкрутити жоден шуруп. Припущення щодо провалу було, що монтаж був виконаний не правильно. Було вирішено провести тестування разом з клієнтом на виробництві. Під час тестування разом з клієнтом визначили що основна проблема полягала в легкій вазі даних ГШ (приблизно 5,30 кг - 1гш). монтажний отвір в самому ГШ був недостатнього розміру для можливості використання більшого ричага. Монтаж з трудом але був виконаний за допомогою насадки для ручного вкручування та з ГШ з буровими коронками. Додатково домовлена розробка та тест ручної насадки під NC 57 сваю та ГШ з подовженою навивкою по конусу.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Організаційний: Проблема та довгий термін виконання виник в зв'язку з зміною планів які не були затверджені та були проговорені лише усною формою. В результаті, рішення яке базувалось на припущенні, призвело до збільшення строків виконання та додаткових витрат. Також не був спланований план дій в разі справдження ризику (В даному випадку неможливість клієнта зробити монтаж). Технічний 1: В результаті було визначено що легкі ГШ (57мм діаметром та 1000мм довжиною) можливо змонтувати вручну лише з додатковими інструментами (монтажна насадки для ручного вкручування, лом) та мінімум двох людей. Технічний 2: ГШ з подовженою по конусу навивкою хоч і показави трохи кращі результати при вкручуванні, є неможливим у реалізіці проєктів великих об'ємів оскільки можливо зробити його лише в ручну. </t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Організаційна: Уникати рішення яке будується на припущенні і за планом є вагомим або фінальним. Якщо припущення стосується технічного аспекту, за можливості проводити попереднє тестування з фіксацією дій та результатів.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>#комунікація #рішення #монтаж #припущення #тестування</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Хома О.</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="50" customHeight="1"/>
     <row r="14" ht="50" customHeight="1"/>
     <row r="15" ht="50" customHeight="1"/>
